--- a/Excel-Student-Performance-Analysis.xlsx
+++ b/Excel-Student-Performance-Analysis.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30606"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE52968B-DCB2-4B9D-9063-D6B393836362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7A36196-D287-4599-A63F-15BCEDECA7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -17,9 +17,14 @@
     <sheet name="Filtering" sheetId="8" r:id="rId7"/>
     <sheet name="Sort and Filter formula " sheetId="9" r:id="rId8"/>
     <sheet name="Data Validation " sheetId="10" r:id="rId9"/>
+    <sheet name="Raw_data2" sheetId="12" r:id="rId10"/>
+    <sheet name="Flash-Fill" sheetId="14" r:id="rId11"/>
+    <sheet name="Remove_Dupllicates" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Filtering!$A$1:$N$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Remove_Dupllicates!$A$2:$E$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Flash-Fill'!$A$2:$K$101</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -67,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3636" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5442" uniqueCount="746">
   <si>
     <t>Student_ID</t>
   </si>
@@ -739,6 +744,1572 @@
   </si>
   <si>
     <t>FAIL</t>
+  </si>
+  <si>
+    <t>Full_Name</t>
+  </si>
+  <si>
+    <t>Class_Gender</t>
+  </si>
+  <si>
+    <t>Subject_Marks</t>
+  </si>
+  <si>
+    <t>ST001</t>
+  </si>
+  <si>
+    <t>10A | Male</t>
+  </si>
+  <si>
+    <t>English:78;Maths:85</t>
+  </si>
+  <si>
+    <t>ST002</t>
+  </si>
+  <si>
+    <t>Ananya Patel</t>
+  </si>
+  <si>
+    <t>10A | Female</t>
+  </si>
+  <si>
+    <t>English:88;Maths:91</t>
+  </si>
+  <si>
+    <t>ST003</t>
+  </si>
+  <si>
+    <t>Rohan Verma</t>
+  </si>
+  <si>
+    <t>10B | Male</t>
+  </si>
+  <si>
+    <t>English:65;Maths:72</t>
+  </si>
+  <si>
+    <t>ST004</t>
+  </si>
+  <si>
+    <t>Priya Singh</t>
+  </si>
+  <si>
+    <t>10B | Female</t>
+  </si>
+  <si>
+    <t>English:91;Maths:89</t>
+  </si>
+  <si>
+    <t>ST005</t>
+  </si>
+  <si>
+    <t>Arjun Mehta</t>
+  </si>
+  <si>
+    <t>English:56;Maths:61</t>
+  </si>
+  <si>
+    <t>ST006</t>
+  </si>
+  <si>
+    <t>Diya Gupta</t>
+  </si>
+  <si>
+    <t>10C | Female</t>
+  </si>
+  <si>
+    <t>English:83;Maths:87</t>
+  </si>
+  <si>
+    <t>ST007</t>
+  </si>
+  <si>
+    <t>Vivaan Shah</t>
+  </si>
+  <si>
+    <t>10C | Male</t>
+  </si>
+  <si>
+    <t>English:72;Maths:68</t>
+  </si>
+  <si>
+    <t>ST008</t>
+  </si>
+  <si>
+    <t>Isha Kumar</t>
+  </si>
+  <si>
+    <t>English:95;Maths:94</t>
+  </si>
+  <si>
+    <t>ST009</t>
+  </si>
+  <si>
+    <t>Aditya Joshi</t>
+  </si>
+  <si>
+    <t>English:48;Maths:55</t>
+  </si>
+  <si>
+    <t>ST010</t>
+  </si>
+  <si>
+    <t>English:79;Maths:82</t>
+  </si>
+  <si>
+    <t>ST011</t>
+  </si>
+  <si>
+    <t>Kabir Rao</t>
+  </si>
+  <si>
+    <t>English:86;Maths:80</t>
+  </si>
+  <si>
+    <t>ST012</t>
+  </si>
+  <si>
+    <t>Sara Khan</t>
+  </si>
+  <si>
+    <t>English:67;Maths:74</t>
+  </si>
+  <si>
+    <t>ST013</t>
+  </si>
+  <si>
+    <t>Reyansh Das</t>
+  </si>
+  <si>
+    <t>English:90;Maths:92</t>
+  </si>
+  <si>
+    <t>ST014</t>
+  </si>
+  <si>
+    <t>Aanya Iyer</t>
+  </si>
+  <si>
+    <t>English:84;Maths:88</t>
+  </si>
+  <si>
+    <t>ST015</t>
+  </si>
+  <si>
+    <t>Ishaan Malhotra</t>
+  </si>
+  <si>
+    <t>English:59;Maths:63</t>
+  </si>
+  <si>
+    <t>ST016</t>
+  </si>
+  <si>
+    <t>Kavya Reddy</t>
+  </si>
+  <si>
+    <t>English:93;Maths:96</t>
+  </si>
+  <si>
+    <t>ST017</t>
+  </si>
+  <si>
+    <t>Dev Mishra</t>
+  </si>
+  <si>
+    <t>English:71;Maths:69</t>
+  </si>
+  <si>
+    <t>ST018</t>
+  </si>
+  <si>
+    <t>Myra Kapoor</t>
+  </si>
+  <si>
+    <t>English:81;Maths:85</t>
+  </si>
+  <si>
+    <t>ST019</t>
+  </si>
+  <si>
+    <t>Krish Bansal</t>
+  </si>
+  <si>
+    <t>English:44;Maths:52</t>
+  </si>
+  <si>
+    <t>ST020</t>
+  </si>
+  <si>
+    <t>Tara Sinha</t>
+  </si>
+  <si>
+    <t>English:87;Maths:90</t>
+  </si>
+  <si>
+    <t>ST021</t>
+  </si>
+  <si>
+    <t>Neil Fernandes</t>
+  </si>
+  <si>
+    <t>English:76;Maths:73</t>
+  </si>
+  <si>
+    <t>ST022</t>
+  </si>
+  <si>
+    <t>Avni Chawla</t>
+  </si>
+  <si>
+    <t>English:89;Maths:92</t>
+  </si>
+  <si>
+    <t>ST023</t>
+  </si>
+  <si>
+    <t>Samar Khanna</t>
+  </si>
+  <si>
+    <t>English:62;Maths:66</t>
+  </si>
+  <si>
+    <t>ST024</t>
+  </si>
+  <si>
+    <t>Riya Menon</t>
+  </si>
+  <si>
+    <t>English:94;Maths:91</t>
+  </si>
+  <si>
+    <t>ST025</t>
+  </si>
+  <si>
+    <t>Atharv Kulkarni</t>
+  </si>
+  <si>
+    <t>English:53;Maths:58</t>
+  </si>
+  <si>
+    <t>ST026</t>
+  </si>
+  <si>
+    <t>Kiara Sethi</t>
+  </si>
+  <si>
+    <t>English:85;Maths:87</t>
+  </si>
+  <si>
+    <t>ST027</t>
+  </si>
+  <si>
+    <t>English:68;Maths:70</t>
+  </si>
+  <si>
+    <t>ST028</t>
+  </si>
+  <si>
+    <t>Pari Desai</t>
+  </si>
+  <si>
+    <t>English:92;Maths:95</t>
+  </si>
+  <si>
+    <t>ST029</t>
+  </si>
+  <si>
+    <t>Om Prakash</t>
+  </si>
+  <si>
+    <t>English:74;Maths:77</t>
+  </si>
+  <si>
+    <t>ST030</t>
+  </si>
+  <si>
+    <t>Siya Jain</t>
+  </si>
+  <si>
+    <t>English:80;Maths:84</t>
+  </si>
+  <si>
+    <t>ST031</t>
+  </si>
+  <si>
+    <t>Manav Arora</t>
+  </si>
+  <si>
+    <t>English:57;Maths:60</t>
+  </si>
+  <si>
+    <t>ST032</t>
+  </si>
+  <si>
+    <t>Navya Bose</t>
+  </si>
+  <si>
+    <t>English:88;Maths:86</t>
+  </si>
+  <si>
+    <t>ST033</t>
+  </si>
+  <si>
+    <t>Aryan Pillai</t>
+  </si>
+  <si>
+    <t>English:69;Maths:71</t>
+  </si>
+  <si>
+    <t>ST034</t>
+  </si>
+  <si>
+    <t>Anika Ghosh</t>
+  </si>
+  <si>
+    <t>English:96;Maths:93</t>
+  </si>
+  <si>
+    <t>ST035</t>
+  </si>
+  <si>
+    <t>Rudra Shetty</t>
+  </si>
+  <si>
+    <t>English:51;Maths:56</t>
+  </si>
+  <si>
+    <t>ST036</t>
+  </si>
+  <si>
+    <t>Mira Saxena</t>
+  </si>
+  <si>
+    <t>English:82;Maths:88</t>
+  </si>
+  <si>
+    <t>ST037</t>
+  </si>
+  <si>
+    <t>Veer Anand</t>
+  </si>
+  <si>
+    <t>English:77;Maths:75</t>
+  </si>
+  <si>
+    <t>ST038</t>
+  </si>
+  <si>
+    <t>Ahana Roy</t>
+  </si>
+  <si>
+    <t>English:90;Maths:94</t>
+  </si>
+  <si>
+    <t>ST039</t>
+  </si>
+  <si>
+    <t>Dhruv Bhatia</t>
+  </si>
+  <si>
+    <t>English:63;Maths:67</t>
+  </si>
+  <si>
+    <t>ST040</t>
+  </si>
+  <si>
+    <t>Saanvi Puri</t>
+  </si>
+  <si>
+    <t>English:86;Maths:89</t>
+  </si>
+  <si>
+    <t>ST041</t>
+  </si>
+  <si>
+    <t>Parth Ahuja</t>
+  </si>
+  <si>
+    <t>English:58;Maths:62</t>
+  </si>
+  <si>
+    <t>ST042</t>
+  </si>
+  <si>
+    <t>Prisha Dutta</t>
+  </si>
+  <si>
+    <t>English:91;Maths:90</t>
+  </si>
+  <si>
+    <t>ST043</t>
+  </si>
+  <si>
+    <t>Kiaan Oberoi</t>
+  </si>
+  <si>
+    <t>English:73;Maths:76</t>
+  </si>
+  <si>
+    <t>ST044</t>
+  </si>
+  <si>
+    <t>Ira Mukherjee</t>
+  </si>
+  <si>
+    <t>English:84;Maths:92</t>
+  </si>
+  <si>
+    <t>ST045</t>
+  </si>
+  <si>
+    <t>Shivansh Sood</t>
+  </si>
+  <si>
+    <t>English:47;Maths:54</t>
+  </si>
+  <si>
+    <t>ST046</t>
+  </si>
+  <si>
+    <t>Trisha Paul</t>
+  </si>
+  <si>
+    <t>English:89;Maths:87</t>
+  </si>
+  <si>
+    <t>ST047</t>
+  </si>
+  <si>
+    <t>Advik Sen</t>
+  </si>
+  <si>
+    <t>English:66;Maths:70</t>
+  </si>
+  <si>
+    <t>ST048</t>
+  </si>
+  <si>
+    <t>Saloni Yadav</t>
+  </si>
+  <si>
+    <t>English:93;Maths:95</t>
+  </si>
+  <si>
+    <t>ST049</t>
+  </si>
+  <si>
+    <t>Hriday Jain</t>
+  </si>
+  <si>
+    <t>English:75;Maths:78</t>
+  </si>
+  <si>
+    <t>ST050</t>
+  </si>
+  <si>
+    <t>Mahi Agarwal</t>
+  </si>
+  <si>
+    <t>English:81;Maths:83</t>
+  </si>
+  <si>
+    <t>ST051</t>
+  </si>
+  <si>
+    <t>Naksh Gill</t>
+  </si>
+  <si>
+    <t>English:55;Maths:59</t>
+  </si>
+  <si>
+    <t>ST052</t>
+  </si>
+  <si>
+    <t>Shanaya Lobo</t>
+  </si>
+  <si>
+    <t>English:87;Maths:91</t>
+  </si>
+  <si>
+    <t>ST053</t>
+  </si>
+  <si>
+    <t>Vihaan Tripathi</t>
+  </si>
+  <si>
+    <t>English:70;Maths:74</t>
+  </si>
+  <si>
+    <t>ST054</t>
+  </si>
+  <si>
+    <t>Akshara Nambiar</t>
+  </si>
+  <si>
+    <t>English:95;Maths:97</t>
+  </si>
+  <si>
+    <t>ST055</t>
+  </si>
+  <si>
+    <t>Rehan Qureshi</t>
+  </si>
+  <si>
+    <t>English:61;Maths:64</t>
+  </si>
+  <si>
+    <t>ST056</t>
+  </si>
+  <si>
+    <t>Aditi Saxena</t>
+  </si>
+  <si>
+    <t>English:83;Maths:86</t>
+  </si>
+  <si>
+    <t>ST057</t>
+  </si>
+  <si>
+    <t>Pranav Suri</t>
+  </si>
+  <si>
+    <t>English:79;Maths:81</t>
+  </si>
+  <si>
+    <t>ST058</t>
+  </si>
+  <si>
+    <t>Simran Kaur</t>
+  </si>
+  <si>
+    <t>English:92;Maths:90</t>
+  </si>
+  <si>
+    <t>ST059</t>
+  </si>
+  <si>
+    <t>Agastya Chandra</t>
+  </si>
+  <si>
+    <t>English:49;Maths:53</t>
+  </si>
+  <si>
+    <t>ST060</t>
+  </si>
+  <si>
+    <t>Anvi Bhardwaj</t>
+  </si>
+  <si>
+    <t>English:85;Maths:88</t>
+  </si>
+  <si>
+    <t>ST061</t>
+  </si>
+  <si>
+    <t>Tejas Patil</t>
+  </si>
+  <si>
+    <t>English:64;Maths:68</t>
+  </si>
+  <si>
+    <t>ST062</t>
+  </si>
+  <si>
+    <t>Ritika Bedi</t>
+  </si>
+  <si>
+    <t>ST063</t>
+  </si>
+  <si>
+    <t>Shaurya Goyal</t>
+  </si>
+  <si>
+    <t>English:72;Maths:75</t>
+  </si>
+  <si>
+    <t>ST064</t>
+  </si>
+  <si>
+    <t>Nitya Venkatesh</t>
+  </si>
+  <si>
+    <t>English:88;Maths:94</t>
+  </si>
+  <si>
+    <t>ST065</t>
+  </si>
+  <si>
+    <t>Arnav Choudhary</t>
+  </si>
+  <si>
+    <t>English:52;Maths:57</t>
+  </si>
+  <si>
+    <t>ST066</t>
+  </si>
+  <si>
+    <t>Pihu Saran</t>
+  </si>
+  <si>
+    <t>English:80;Maths:85</t>
+  </si>
+  <si>
+    <t>ST067</t>
+  </si>
+  <si>
+    <t>Anshul Tiwari</t>
+  </si>
+  <si>
+    <t>English:67;Maths:69</t>
+  </si>
+  <si>
+    <t>ST068</t>
+  </si>
+  <si>
+    <t>Salma Sheikh</t>
+  </si>
+  <si>
+    <t>English:94;Maths:96</t>
+  </si>
+  <si>
+    <t>ST069</t>
+  </si>
+  <si>
+    <t>Kushagra Mittal</t>
+  </si>
+  <si>
+    <t>English:76;Maths:79</t>
+  </si>
+  <si>
+    <t>ST070</t>
+  </si>
+  <si>
+    <t>Jhanvi Parmar</t>
+  </si>
+  <si>
+    <t>ST071</t>
+  </si>
+  <si>
+    <t>Raghav Batra</t>
+  </si>
+  <si>
+    <t>English:60;Maths:65</t>
+  </si>
+  <si>
+    <t>ST072</t>
+  </si>
+  <si>
+    <t>Shruti Naidu</t>
+  </si>
+  <si>
+    <t>English:91;Maths:93</t>
+  </si>
+  <si>
+    <t>ST073</t>
+  </si>
+  <si>
+    <t>Abeer Lal</t>
+  </si>
+  <si>
+    <t>English:74;Maths:72</t>
+  </si>
+  <si>
+    <t>ST074</t>
+  </si>
+  <si>
+    <t>Muskan Saini</t>
+  </si>
+  <si>
+    <t>English:84;Maths:87</t>
+  </si>
+  <si>
+    <t>ST075</t>
+  </si>
+  <si>
+    <t>Chirag Wadhwa</t>
+  </si>
+  <si>
+    <t>English:46;Maths:51</t>
+  </si>
+  <si>
+    <t>ST076</t>
+  </si>
+  <si>
+    <t>Vanya Sood</t>
+  </si>
+  <si>
+    <t>ST077</t>
+  </si>
+  <si>
+    <t>Pratyush Roy</t>
+  </si>
+  <si>
+    <t>English:68;Maths:73</t>
+  </si>
+  <si>
+    <t>ST078</t>
+  </si>
+  <si>
+    <t>Khushi Arora</t>
+  </si>
+  <si>
+    <t>English:96;Maths:98</t>
+  </si>
+  <si>
+    <t>ST079</t>
+  </si>
+  <si>
+    <t>Naman Bhat</t>
+  </si>
+  <si>
+    <t>English:57;Maths:61</t>
+  </si>
+  <si>
+    <t>ST080</t>
+  </si>
+  <si>
+    <t>Shreya Iyer</t>
+  </si>
+  <si>
+    <t>English:82;Maths:84</t>
+  </si>
+  <si>
+    <t>ST081</t>
+  </si>
+  <si>
+    <t>ST082</t>
+  </si>
+  <si>
+    <t>ST083</t>
+  </si>
+  <si>
+    <t>ST084</t>
+  </si>
+  <si>
+    <t>ST085</t>
+  </si>
+  <si>
+    <t>Aarav  Sharma</t>
+  </si>
+  <si>
+    <t>ST086</t>
+  </si>
+  <si>
+    <t>ROHAN VERMA</t>
+  </si>
+  <si>
+    <t>ST087</t>
+  </si>
+  <si>
+    <t>ST088</t>
+  </si>
+  <si>
+    <t>ST089</t>
+  </si>
+  <si>
+    <t>ST090</t>
+  </si>
+  <si>
+    <t>ST091</t>
+  </si>
+  <si>
+    <t>ST092</t>
+  </si>
+  <si>
+    <t>ST093</t>
+  </si>
+  <si>
+    <t>ST094</t>
+  </si>
+  <si>
+    <t>English:75;Maths:80</t>
+  </si>
+  <si>
+    <t>ST095</t>
+  </si>
+  <si>
+    <t>ST096</t>
+  </si>
+  <si>
+    <t>ST097</t>
+  </si>
+  <si>
+    <t>ST098</t>
+  </si>
+  <si>
+    <t>ST099</t>
+  </si>
+  <si>
+    <t>ST100</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Aarav</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>English:78</t>
+  </si>
+  <si>
+    <t>Maths:85</t>
+  </si>
+  <si>
+    <t>Ananya</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>English:88</t>
+  </si>
+  <si>
+    <t>Maths:91</t>
+  </si>
+  <si>
+    <t>Rohan</t>
+  </si>
+  <si>
+    <t>Verma</t>
+  </si>
+  <si>
+    <t>English:65</t>
+  </si>
+  <si>
+    <t>Maths:72</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Singh</t>
+  </si>
+  <si>
+    <t>English:91</t>
+  </si>
+  <si>
+    <t>Maths:89</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Mehta</t>
+  </si>
+  <si>
+    <t>English:56</t>
+  </si>
+  <si>
+    <t>Maths:61</t>
+  </si>
+  <si>
+    <t>Diya</t>
+  </si>
+  <si>
+    <t>Gupta</t>
+  </si>
+  <si>
+    <t>English:83</t>
+  </si>
+  <si>
+    <t>Maths:87</t>
+  </si>
+  <si>
+    <t>Vivaan</t>
+  </si>
+  <si>
+    <t>Shah</t>
+  </si>
+  <si>
+    <t>English:72</t>
+  </si>
+  <si>
+    <t>Maths:68</t>
+  </si>
+  <si>
+    <t>Isha</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>English:95</t>
+  </si>
+  <si>
+    <t>Maths:94</t>
+  </si>
+  <si>
+    <t>Aditya</t>
+  </si>
+  <si>
+    <t>Joshi</t>
+  </si>
+  <si>
+    <t>English:48</t>
+  </si>
+  <si>
+    <t>Maths:55</t>
+  </si>
+  <si>
+    <t>Meera</t>
+  </si>
+  <si>
+    <t>Nair</t>
+  </si>
+  <si>
+    <t>English:79</t>
+  </si>
+  <si>
+    <t>Maths:82</t>
+  </si>
+  <si>
+    <t>Kabir</t>
+  </si>
+  <si>
+    <t>Rao</t>
+  </si>
+  <si>
+    <t>English:86</t>
+  </si>
+  <si>
+    <t>Maths:80</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Khan</t>
+  </si>
+  <si>
+    <t>English:67</t>
+  </si>
+  <si>
+    <t>Maths:74</t>
+  </si>
+  <si>
+    <t>Reyansh</t>
+  </si>
+  <si>
+    <t>Das</t>
+  </si>
+  <si>
+    <t>English:90</t>
+  </si>
+  <si>
+    <t>Maths:92</t>
+  </si>
+  <si>
+    <t>Aanya</t>
+  </si>
+  <si>
+    <t>Iyer</t>
+  </si>
+  <si>
+    <t>English:84</t>
+  </si>
+  <si>
+    <t>Maths:88</t>
+  </si>
+  <si>
+    <t>Ishaan</t>
+  </si>
+  <si>
+    <t>Malhotra</t>
+  </si>
+  <si>
+    <t>English:59</t>
+  </si>
+  <si>
+    <t>Maths:63</t>
+  </si>
+  <si>
+    <t>Kavya</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>English:93</t>
+  </si>
+  <si>
+    <t>Maths:96</t>
+  </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>Mishra</t>
+  </si>
+  <si>
+    <t>English:71</t>
+  </si>
+  <si>
+    <t>Maths:69</t>
+  </si>
+  <si>
+    <t>Myra</t>
+  </si>
+  <si>
+    <t>Kapoor</t>
+  </si>
+  <si>
+    <t>English:81</t>
+  </si>
+  <si>
+    <t>Krish</t>
+  </si>
+  <si>
+    <t>Bansal</t>
+  </si>
+  <si>
+    <t>English:44</t>
+  </si>
+  <si>
+    <t>Maths:52</t>
+  </si>
+  <si>
+    <t>Tara</t>
+  </si>
+  <si>
+    <t>Sinha</t>
+  </si>
+  <si>
+    <t>English:87</t>
+  </si>
+  <si>
+    <t>Maths:90</t>
+  </si>
+  <si>
+    <t>Neil</t>
+  </si>
+  <si>
+    <t>Fernandes</t>
+  </si>
+  <si>
+    <t>English:76</t>
+  </si>
+  <si>
+    <t>Maths:73</t>
+  </si>
+  <si>
+    <t>Avni</t>
+  </si>
+  <si>
+    <t>Chawla</t>
+  </si>
+  <si>
+    <t>English:89</t>
+  </si>
+  <si>
+    <t>Samar</t>
+  </si>
+  <si>
+    <t>Khanna</t>
+  </si>
+  <si>
+    <t>English:62</t>
+  </si>
+  <si>
+    <t>Maths:66</t>
+  </si>
+  <si>
+    <t>Riya</t>
+  </si>
+  <si>
+    <t>Menon</t>
+  </si>
+  <si>
+    <t>English:94</t>
+  </si>
+  <si>
+    <t>Atharv</t>
+  </si>
+  <si>
+    <t>Kulkarni</t>
+  </si>
+  <si>
+    <t>English:53</t>
+  </si>
+  <si>
+    <t>Maths:58</t>
+  </si>
+  <si>
+    <t>Kiara</t>
+  </si>
+  <si>
+    <t>Sethi</t>
+  </si>
+  <si>
+    <t>English:85</t>
+  </si>
+  <si>
+    <t>Yash</t>
+  </si>
+  <si>
+    <t>Thakur</t>
+  </si>
+  <si>
+    <t>English:68</t>
+  </si>
+  <si>
+    <t>Maths:70</t>
+  </si>
+  <si>
+    <t>Pari</t>
+  </si>
+  <si>
+    <t>Desai</t>
+  </si>
+  <si>
+    <t>English:92</t>
+  </si>
+  <si>
+    <t>Maths:95</t>
+  </si>
+  <si>
+    <t>Om</t>
+  </si>
+  <si>
+    <t>Prakash</t>
+  </si>
+  <si>
+    <t>English:74</t>
+  </si>
+  <si>
+    <t>Maths:77</t>
+  </si>
+  <si>
+    <t>Siya</t>
+  </si>
+  <si>
+    <t>Jain</t>
+  </si>
+  <si>
+    <t>English:80</t>
+  </si>
+  <si>
+    <t>Maths:84</t>
+  </si>
+  <si>
+    <t>Manav</t>
+  </si>
+  <si>
+    <t>Arora</t>
+  </si>
+  <si>
+    <t>English:57</t>
+  </si>
+  <si>
+    <t>Maths:60</t>
+  </si>
+  <si>
+    <t>Navya</t>
+  </si>
+  <si>
+    <t>Bose</t>
+  </si>
+  <si>
+    <t>Maths:86</t>
+  </si>
+  <si>
+    <t>Aryan</t>
+  </si>
+  <si>
+    <t>Pillai</t>
+  </si>
+  <si>
+    <t>English:69</t>
+  </si>
+  <si>
+    <t>Maths:71</t>
+  </si>
+  <si>
+    <t>Anika</t>
+  </si>
+  <si>
+    <t>Ghosh</t>
+  </si>
+  <si>
+    <t>English:96</t>
+  </si>
+  <si>
+    <t>Maths:93</t>
+  </si>
+  <si>
+    <t>Rudra</t>
+  </si>
+  <si>
+    <t>Shetty</t>
+  </si>
+  <si>
+    <t>English:51</t>
+  </si>
+  <si>
+    <t>Maths:56</t>
+  </si>
+  <si>
+    <t>Mira</t>
+  </si>
+  <si>
+    <t>Saxena</t>
+  </si>
+  <si>
+    <t>English:82</t>
+  </si>
+  <si>
+    <t>Veer</t>
+  </si>
+  <si>
+    <t>Anand</t>
+  </si>
+  <si>
+    <t>English:77</t>
+  </si>
+  <si>
+    <t>Maths:75</t>
+  </si>
+  <si>
+    <t>Ahana</t>
+  </si>
+  <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>Dhruv</t>
+  </si>
+  <si>
+    <t>Bhatia</t>
+  </si>
+  <si>
+    <t>English:63</t>
+  </si>
+  <si>
+    <t>Maths:67</t>
+  </si>
+  <si>
+    <t>Saanvi</t>
+  </si>
+  <si>
+    <t>Puri</t>
+  </si>
+  <si>
+    <t>Parth</t>
+  </si>
+  <si>
+    <t>Ahuja</t>
+  </si>
+  <si>
+    <t>English:58</t>
+  </si>
+  <si>
+    <t>Maths:62</t>
+  </si>
+  <si>
+    <t>Prisha</t>
+  </si>
+  <si>
+    <t>Dutta</t>
+  </si>
+  <si>
+    <t>Kiaan</t>
+  </si>
+  <si>
+    <t>Oberoi</t>
+  </si>
+  <si>
+    <t>English:73</t>
+  </si>
+  <si>
+    <t>Maths:76</t>
+  </si>
+  <si>
+    <t>Ira</t>
+  </si>
+  <si>
+    <t>Mukherjee</t>
+  </si>
+  <si>
+    <t>Shivansh</t>
+  </si>
+  <si>
+    <t>Sood</t>
+  </si>
+  <si>
+    <t>English:47</t>
+  </si>
+  <si>
+    <t>Maths:54</t>
+  </si>
+  <si>
+    <t>Trisha</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Advik</t>
+  </si>
+  <si>
+    <t>Sen</t>
+  </si>
+  <si>
+    <t>English:66</t>
+  </si>
+  <si>
+    <t>Saloni</t>
+  </si>
+  <si>
+    <t>Yadav</t>
+  </si>
+  <si>
+    <t>Hriday</t>
+  </si>
+  <si>
+    <t>English:75</t>
+  </si>
+  <si>
+    <t>Maths:78</t>
+  </si>
+  <si>
+    <t>Mahi</t>
+  </si>
+  <si>
+    <t>Agarwal</t>
+  </si>
+  <si>
+    <t>Maths:83</t>
+  </si>
+  <si>
+    <t>Naksh</t>
+  </si>
+  <si>
+    <t>Gill</t>
+  </si>
+  <si>
+    <t>English:55</t>
+  </si>
+  <si>
+    <t>Maths:59</t>
+  </si>
+  <si>
+    <t>Shanaya</t>
+  </si>
+  <si>
+    <t>Lobo</t>
+  </si>
+  <si>
+    <t>Vihaan</t>
+  </si>
+  <si>
+    <t>Tripathi</t>
+  </si>
+  <si>
+    <t>English:70</t>
+  </si>
+  <si>
+    <t>Akshara</t>
+  </si>
+  <si>
+    <t>Nambiar</t>
+  </si>
+  <si>
+    <t>Maths:97</t>
+  </si>
+  <si>
+    <t>Rehan</t>
+  </si>
+  <si>
+    <t>Qureshi</t>
+  </si>
+  <si>
+    <t>English:61</t>
+  </si>
+  <si>
+    <t>Maths:64</t>
+  </si>
+  <si>
+    <t>Aditi</t>
+  </si>
+  <si>
+    <t>Pranav</t>
+  </si>
+  <si>
+    <t>Suri</t>
+  </si>
+  <si>
+    <t>Maths:81</t>
+  </si>
+  <si>
+    <t>Simran</t>
+  </si>
+  <si>
+    <t>Kaur</t>
+  </si>
+  <si>
+    <t>Agastya</t>
+  </si>
+  <si>
+    <t>Chandra</t>
+  </si>
+  <si>
+    <t>English:49</t>
+  </si>
+  <si>
+    <t>Maths:53</t>
+  </si>
+  <si>
+    <t>Anvi</t>
+  </si>
+  <si>
+    <t>Bhardwaj</t>
+  </si>
+  <si>
+    <t>Tejas</t>
+  </si>
+  <si>
+    <t>Patil</t>
+  </si>
+  <si>
+    <t>English:64</t>
+  </si>
+  <si>
+    <t>Ritika</t>
+  </si>
+  <si>
+    <t>Bedi</t>
+  </si>
+  <si>
+    <t>Shaurya</t>
+  </si>
+  <si>
+    <t>Goyal</t>
+  </si>
+  <si>
+    <t>Nitya</t>
+  </si>
+  <si>
+    <t>Venkatesh</t>
+  </si>
+  <si>
+    <t>Arnav</t>
+  </si>
+  <si>
+    <t>Choudhary</t>
+  </si>
+  <si>
+    <t>English:52</t>
+  </si>
+  <si>
+    <t>Maths:57</t>
+  </si>
+  <si>
+    <t>Pihu</t>
+  </si>
+  <si>
+    <t>Saran</t>
+  </si>
+  <si>
+    <t>Anshul</t>
+  </si>
+  <si>
+    <t>Tiwari</t>
+  </si>
+  <si>
+    <t>Salma</t>
+  </si>
+  <si>
+    <t>Sheikh</t>
+  </si>
+  <si>
+    <t>Kushagra</t>
+  </si>
+  <si>
+    <t>Mittal</t>
+  </si>
+  <si>
+    <t>Maths:79</t>
+  </si>
+  <si>
+    <t>Jhanvi</t>
+  </si>
+  <si>
+    <t>Parmar</t>
+  </si>
+  <si>
+    <t>Raghav</t>
+  </si>
+  <si>
+    <t>Batra</t>
+  </si>
+  <si>
+    <t>English:60</t>
+  </si>
+  <si>
+    <t>Maths:65</t>
+  </si>
+  <si>
+    <t>Shruti</t>
+  </si>
+  <si>
+    <t>Naidu</t>
+  </si>
+  <si>
+    <t>Abeer</t>
+  </si>
+  <si>
+    <t>Lal</t>
+  </si>
+  <si>
+    <t>Muskan</t>
+  </si>
+  <si>
+    <t>Saini</t>
+  </si>
+  <si>
+    <t>Chirag</t>
+  </si>
+  <si>
+    <t>Wadhwa</t>
+  </si>
+  <si>
+    <t>English:46</t>
+  </si>
+  <si>
+    <t>Maths:51</t>
+  </si>
+  <si>
+    <t>Vanya</t>
+  </si>
+  <si>
+    <t>Pratyush</t>
+  </si>
+  <si>
+    <t>Khushi</t>
+  </si>
+  <si>
+    <t>Maths:98</t>
+  </si>
+  <si>
+    <t>Naman</t>
+  </si>
+  <si>
+    <t>Bhat</t>
+  </si>
+  <si>
+    <t>Shreya</t>
+  </si>
+  <si>
+    <t>ROHAN</t>
+  </si>
+  <si>
+    <t>VERMA</t>
   </si>
 </sst>
 </file>
@@ -810,7 +2381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -854,6 +2425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4149,6 +5721,6959 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E22588E-4B9C-4D90-AC36-AFF9F1B9A26B}">
+  <dimension ref="A2:E102"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="23.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="26.25" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="19">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="19">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B13" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E13" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" t="s">
+        <v>266</v>
+      </c>
+      <c r="E14" s="19">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D15" t="s">
+        <v>269</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" t="s">
+        <v>251</v>
+      </c>
+      <c r="D19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" s="19">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" t="s">
+        <v>287</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" t="s">
+        <v>289</v>
+      </c>
+      <c r="C22" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" t="s">
+        <v>290</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>291</v>
+      </c>
+      <c r="B23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23" t="s">
+        <v>293</v>
+      </c>
+      <c r="E23" s="19">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B24" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" t="s">
+        <v>296</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" t="s">
+        <v>251</v>
+      </c>
+      <c r="D25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25" s="19">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B26" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" t="s">
+        <v>232</v>
+      </c>
+      <c r="D26" t="s">
+        <v>302</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>303</v>
+      </c>
+      <c r="B27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27" t="s">
+        <v>236</v>
+      </c>
+      <c r="D27" t="s">
+        <v>305</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>306</v>
+      </c>
+      <c r="B28" t="s">
+        <v>307</v>
+      </c>
+      <c r="C28" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" t="s">
+        <v>308</v>
+      </c>
+      <c r="E28" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" t="s">
+        <v>310</v>
+      </c>
+      <c r="E29" s="19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>311</v>
+      </c>
+      <c r="B30" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>314</v>
+      </c>
+      <c r="B31" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" t="s">
+        <v>316</v>
+      </c>
+      <c r="E31" s="19">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" t="s">
+        <v>319</v>
+      </c>
+      <c r="E32" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>320</v>
+      </c>
+      <c r="B33" t="s">
+        <v>321</v>
+      </c>
+      <c r="C33" t="s">
+        <v>236</v>
+      </c>
+      <c r="D33" t="s">
+        <v>322</v>
+      </c>
+      <c r="E33" s="19">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" t="s">
+        <v>325</v>
+      </c>
+      <c r="E34" s="19">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" t="s">
+        <v>327</v>
+      </c>
+      <c r="C35" t="s">
+        <v>228</v>
+      </c>
+      <c r="D35" t="s">
+        <v>328</v>
+      </c>
+      <c r="E35" s="19">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" t="s">
+        <v>330</v>
+      </c>
+      <c r="C36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" t="s">
+        <v>331</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>332</v>
+      </c>
+      <c r="B37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C37" t="s">
+        <v>251</v>
+      </c>
+      <c r="D37" t="s">
+        <v>334</v>
+      </c>
+      <c r="E37" s="19">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>335</v>
+      </c>
+      <c r="B38" t="s">
+        <v>336</v>
+      </c>
+      <c r="C38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D38" t="s">
+        <v>337</v>
+      </c>
+      <c r="E38" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" t="s">
+        <v>339</v>
+      </c>
+      <c r="C39" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" t="s">
+        <v>340</v>
+      </c>
+      <c r="E39" s="19">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>341</v>
+      </c>
+      <c r="B40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" t="s">
+        <v>343</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>344</v>
+      </c>
+      <c r="B41" t="s">
+        <v>345</v>
+      </c>
+      <c r="C41" t="s">
+        <v>228</v>
+      </c>
+      <c r="D41" t="s">
+        <v>346</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>347</v>
+      </c>
+      <c r="B42" t="s">
+        <v>348</v>
+      </c>
+      <c r="C42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" t="s">
+        <v>349</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>350</v>
+      </c>
+      <c r="B43" t="s">
+        <v>351</v>
+      </c>
+      <c r="C43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D43" t="s">
+        <v>352</v>
+      </c>
+      <c r="E43" s="19">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>353</v>
+      </c>
+      <c r="B44" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" t="s">
+        <v>232</v>
+      </c>
+      <c r="D44" t="s">
+        <v>355</v>
+      </c>
+      <c r="E44" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>356</v>
+      </c>
+      <c r="B45" t="s">
+        <v>357</v>
+      </c>
+      <c r="C45" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" t="s">
+        <v>358</v>
+      </c>
+      <c r="E45" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>359</v>
+      </c>
+      <c r="B46" t="s">
+        <v>360</v>
+      </c>
+      <c r="C46" t="s">
+        <v>247</v>
+      </c>
+      <c r="D46" t="s">
+        <v>361</v>
+      </c>
+      <c r="E46" s="19">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>362</v>
+      </c>
+      <c r="B47" t="s">
+        <v>363</v>
+      </c>
+      <c r="C47" t="s">
+        <v>228</v>
+      </c>
+      <c r="D47" t="s">
+        <v>364</v>
+      </c>
+      <c r="E47" s="19">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>365</v>
+      </c>
+      <c r="B48" t="s">
+        <v>366</v>
+      </c>
+      <c r="C48" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" t="s">
+        <v>367</v>
+      </c>
+      <c r="E48" s="19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>368</v>
+      </c>
+      <c r="B49" t="s">
+        <v>369</v>
+      </c>
+      <c r="C49" t="s">
+        <v>251</v>
+      </c>
+      <c r="D49" t="s">
+        <v>370</v>
+      </c>
+      <c r="E49" s="19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>371</v>
+      </c>
+      <c r="B50" t="s">
+        <v>372</v>
+      </c>
+      <c r="C50" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" t="s">
+        <v>373</v>
+      </c>
+      <c r="E50" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>374</v>
+      </c>
+      <c r="B51" t="s">
+        <v>375</v>
+      </c>
+      <c r="C51" t="s">
+        <v>236</v>
+      </c>
+      <c r="D51" t="s">
+        <v>376</v>
+      </c>
+      <c r="E51" s="19">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s">
+        <v>378</v>
+      </c>
+      <c r="C52" t="s">
+        <v>247</v>
+      </c>
+      <c r="D52" t="s">
+        <v>379</v>
+      </c>
+      <c r="E52" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>380</v>
+      </c>
+      <c r="B53" t="s">
+        <v>381</v>
+      </c>
+      <c r="C53" t="s">
+        <v>228</v>
+      </c>
+      <c r="D53" t="s">
+        <v>382</v>
+      </c>
+      <c r="E53" s="19">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>383</v>
+      </c>
+      <c r="B54" t="s">
+        <v>384</v>
+      </c>
+      <c r="C54" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" t="s">
+        <v>385</v>
+      </c>
+      <c r="E54" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>386</v>
+      </c>
+      <c r="B55" t="s">
+        <v>387</v>
+      </c>
+      <c r="C55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D55" t="s">
+        <v>388</v>
+      </c>
+      <c r="E55" s="19">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>389</v>
+      </c>
+      <c r="B56" t="s">
+        <v>390</v>
+      </c>
+      <c r="C56" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" t="s">
+        <v>391</v>
+      </c>
+      <c r="E56" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>392</v>
+      </c>
+      <c r="B57" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" t="s">
+        <v>394</v>
+      </c>
+      <c r="E57" s="19">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>395</v>
+      </c>
+      <c r="B58" t="s">
+        <v>396</v>
+      </c>
+      <c r="C58" t="s">
+        <v>247</v>
+      </c>
+      <c r="D58" t="s">
+        <v>397</v>
+      </c>
+      <c r="E58" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>398</v>
+      </c>
+      <c r="B59" t="s">
+        <v>399</v>
+      </c>
+      <c r="C59" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" t="s">
+        <v>400</v>
+      </c>
+      <c r="E59" s="19">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>401</v>
+      </c>
+      <c r="B60" t="s">
+        <v>402</v>
+      </c>
+      <c r="C60" t="s">
+        <v>240</v>
+      </c>
+      <c r="D60" t="s">
+        <v>403</v>
+      </c>
+      <c r="E60" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>404</v>
+      </c>
+      <c r="B61" t="s">
+        <v>405</v>
+      </c>
+      <c r="C61" t="s">
+        <v>251</v>
+      </c>
+      <c r="D61" t="s">
+        <v>406</v>
+      </c>
+      <c r="E61" s="19">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>407</v>
+      </c>
+      <c r="B62" t="s">
+        <v>408</v>
+      </c>
+      <c r="C62" t="s">
+        <v>232</v>
+      </c>
+      <c r="D62" t="s">
+        <v>409</v>
+      </c>
+      <c r="E62" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>410</v>
+      </c>
+      <c r="B63" t="s">
+        <v>411</v>
+      </c>
+      <c r="C63" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" t="s">
+        <v>412</v>
+      </c>
+      <c r="E63" s="19">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>413</v>
+      </c>
+      <c r="B64" t="s">
+        <v>414</v>
+      </c>
+      <c r="C64" t="s">
+        <v>247</v>
+      </c>
+      <c r="D64" t="s">
+        <v>269</v>
+      </c>
+      <c r="E64" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>415</v>
+      </c>
+      <c r="B65" t="s">
+        <v>416</v>
+      </c>
+      <c r="C65" t="s">
+        <v>228</v>
+      </c>
+      <c r="D65" t="s">
+        <v>417</v>
+      </c>
+      <c r="E65" s="19">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>418</v>
+      </c>
+      <c r="B66" t="s">
+        <v>419</v>
+      </c>
+      <c r="C66" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" t="s">
+        <v>420</v>
+      </c>
+      <c r="E66" s="19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>421</v>
+      </c>
+      <c r="B67" t="s">
+        <v>422</v>
+      </c>
+      <c r="C67" t="s">
+        <v>251</v>
+      </c>
+      <c r="D67" t="s">
+        <v>423</v>
+      </c>
+      <c r="E67" s="19">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>424</v>
+      </c>
+      <c r="B68" t="s">
+        <v>425</v>
+      </c>
+      <c r="C68" t="s">
+        <v>232</v>
+      </c>
+      <c r="D68" t="s">
+        <v>426</v>
+      </c>
+      <c r="E68" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>427</v>
+      </c>
+      <c r="B69" t="s">
+        <v>428</v>
+      </c>
+      <c r="C69" t="s">
+        <v>236</v>
+      </c>
+      <c r="D69" t="s">
+        <v>429</v>
+      </c>
+      <c r="E69" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>430</v>
+      </c>
+      <c r="B70" t="s">
+        <v>431</v>
+      </c>
+      <c r="C70" t="s">
+        <v>247</v>
+      </c>
+      <c r="D70" t="s">
+        <v>432</v>
+      </c>
+      <c r="E70" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>433</v>
+      </c>
+      <c r="B71" t="s">
+        <v>434</v>
+      </c>
+      <c r="C71" t="s">
+        <v>228</v>
+      </c>
+      <c r="D71" t="s">
+        <v>435</v>
+      </c>
+      <c r="E71" s="19">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>436</v>
+      </c>
+      <c r="B72" t="s">
+        <v>437</v>
+      </c>
+      <c r="C72" t="s">
+        <v>240</v>
+      </c>
+      <c r="D72" t="s">
+        <v>349</v>
+      </c>
+      <c r="E72" s="19">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>438</v>
+      </c>
+      <c r="B73" t="s">
+        <v>439</v>
+      </c>
+      <c r="C73" t="s">
+        <v>251</v>
+      </c>
+      <c r="D73" t="s">
+        <v>440</v>
+      </c>
+      <c r="E73" s="19">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>441</v>
+      </c>
+      <c r="B74" t="s">
+        <v>442</v>
+      </c>
+      <c r="C74" t="s">
+        <v>232</v>
+      </c>
+      <c r="D74" t="s">
+        <v>443</v>
+      </c>
+      <c r="E74" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>444</v>
+      </c>
+      <c r="B75" t="s">
+        <v>445</v>
+      </c>
+      <c r="C75" t="s">
+        <v>236</v>
+      </c>
+      <c r="D75" t="s">
+        <v>446</v>
+      </c>
+      <c r="E75" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>447</v>
+      </c>
+      <c r="B76" t="s">
+        <v>448</v>
+      </c>
+      <c r="C76" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76" t="s">
+        <v>449</v>
+      </c>
+      <c r="E76" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>450</v>
+      </c>
+      <c r="B77" t="s">
+        <v>451</v>
+      </c>
+      <c r="C77" t="s">
+        <v>228</v>
+      </c>
+      <c r="D77" t="s">
+        <v>452</v>
+      </c>
+      <c r="E77" s="19">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>453</v>
+      </c>
+      <c r="B78" t="s">
+        <v>454</v>
+      </c>
+      <c r="C78" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" t="s">
+        <v>296</v>
+      </c>
+      <c r="E78" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>455</v>
+      </c>
+      <c r="B79" t="s">
+        <v>456</v>
+      </c>
+      <c r="C79" t="s">
+        <v>251</v>
+      </c>
+      <c r="D79" t="s">
+        <v>457</v>
+      </c>
+      <c r="E79" s="19">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>458</v>
+      </c>
+      <c r="B80" t="s">
+        <v>459</v>
+      </c>
+      <c r="C80" t="s">
+        <v>232</v>
+      </c>
+      <c r="D80" t="s">
+        <v>460</v>
+      </c>
+      <c r="E80" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>461</v>
+      </c>
+      <c r="B81" t="s">
+        <v>462</v>
+      </c>
+      <c r="C81" t="s">
+        <v>236</v>
+      </c>
+      <c r="D81" t="s">
+        <v>463</v>
+      </c>
+      <c r="E81" s="19">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>464</v>
+      </c>
+      <c r="B82" t="s">
+        <v>465</v>
+      </c>
+      <c r="C82" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82" t="s">
+        <v>466</v>
+      </c>
+      <c r="E82" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>467</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>468</v>
+      </c>
+      <c r="B84" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" t="s">
+        <v>232</v>
+      </c>
+      <c r="D84" t="s">
+        <v>233</v>
+      </c>
+      <c r="E84" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>469</v>
+      </c>
+      <c r="B85" t="s">
+        <v>235</v>
+      </c>
+      <c r="C85" t="s">
+        <v>236</v>
+      </c>
+      <c r="D85" t="s">
+        <v>237</v>
+      </c>
+      <c r="E85" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>470</v>
+      </c>
+      <c r="B86" t="s">
+        <v>239</v>
+      </c>
+      <c r="C86" t="s">
+        <v>240</v>
+      </c>
+      <c r="D86" t="s">
+        <v>241</v>
+      </c>
+      <c r="E86" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>471</v>
+      </c>
+      <c r="B87" t="s">
+        <v>472</v>
+      </c>
+      <c r="C87" t="s">
+        <v>228</v>
+      </c>
+      <c r="D87" t="s">
+        <v>229</v>
+      </c>
+      <c r="E87" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>473</v>
+      </c>
+      <c r="B88" t="s">
+        <v>474</v>
+      </c>
+      <c r="C88" t="s">
+        <v>236</v>
+      </c>
+      <c r="D88" t="s">
+        <v>237</v>
+      </c>
+      <c r="E88" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>475</v>
+      </c>
+      <c r="B89" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" t="s">
+        <v>232</v>
+      </c>
+      <c r="D89" t="s">
+        <v>233</v>
+      </c>
+      <c r="E89" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>476</v>
+      </c>
+      <c r="B90" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" t="s">
+        <v>240</v>
+      </c>
+      <c r="D90" t="s">
+        <v>241</v>
+      </c>
+      <c r="E90" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>477</v>
+      </c>
+      <c r="B91" t="s">
+        <v>262</v>
+      </c>
+      <c r="C91" t="s">
+        <v>251</v>
+      </c>
+      <c r="D91" t="s">
+        <v>263</v>
+      </c>
+      <c r="E91" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>478</v>
+      </c>
+      <c r="B92" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" t="s">
+        <v>240</v>
+      </c>
+      <c r="D92" t="s">
+        <v>260</v>
+      </c>
+      <c r="E92" s="19">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>479</v>
+      </c>
+      <c r="B93" t="s">
+        <v>231</v>
+      </c>
+      <c r="C93" t="s">
+        <v>232</v>
+      </c>
+      <c r="D93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E93" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>480</v>
+      </c>
+      <c r="B94" t="s">
+        <v>235</v>
+      </c>
+      <c r="C94" t="s">
+        <v>236</v>
+      </c>
+      <c r="D94" t="s">
+        <v>237</v>
+      </c>
+      <c r="E94" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>481</v>
+      </c>
+      <c r="B95" t="s">
+        <v>246</v>
+      </c>
+      <c r="C95" t="s">
+        <v>247</v>
+      </c>
+      <c r="D95" t="s">
+        <v>248</v>
+      </c>
+      <c r="E95" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>482</v>
+      </c>
+      <c r="C96" t="s">
+        <v>232</v>
+      </c>
+      <c r="D96" t="s">
+        <v>483</v>
+      </c>
+      <c r="E96" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>484</v>
+      </c>
+      <c r="B97" t="s">
+        <v>250</v>
+      </c>
+      <c r="C97" t="s">
+        <v>251</v>
+      </c>
+      <c r="D97" t="s">
+        <v>252</v>
+      </c>
+      <c r="E97" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>485</v>
+      </c>
+      <c r="B98" t="s">
+        <v>254</v>
+      </c>
+      <c r="C98" t="s">
+        <v>232</v>
+      </c>
+      <c r="D98" t="s">
+        <v>255</v>
+      </c>
+      <c r="E98" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>486</v>
+      </c>
+      <c r="B99" t="s">
+        <v>243</v>
+      </c>
+      <c r="C99" t="s">
+        <v>228</v>
+      </c>
+      <c r="D99" t="s">
+        <v>244</v>
+      </c>
+      <c r="E99" s="19">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>487</v>
+      </c>
+      <c r="B100" t="s">
+        <v>246</v>
+      </c>
+      <c r="C100" t="s">
+        <v>247</v>
+      </c>
+      <c r="D100" t="s">
+        <v>248</v>
+      </c>
+      <c r="E100" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>488</v>
+      </c>
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" t="s">
+        <v>228</v>
+      </c>
+      <c r="D101" t="s">
+        <v>229</v>
+      </c>
+      <c r="E101" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>489</v>
+      </c>
+      <c r="B102" t="s">
+        <v>268</v>
+      </c>
+      <c r="C102" t="s">
+        <v>236</v>
+      </c>
+      <c r="D102" t="s">
+        <v>269</v>
+      </c>
+      <c r="E102" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44B60CC-E833-4AB7-B399-324647D0EF1C}">
+  <dimension ref="A2:K101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="11" width="23.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" ht="26.25" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="K20" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="K21" s="6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="K22" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="K23" s="6">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="K24" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="K25" s="6">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="K26" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="K28" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="K29" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="K30" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="K38" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="K39" s="6">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="K40" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="K41" s="6">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="K42" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="K43" s="6">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="K44" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="K45" s="6">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="K46" s="6">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="K47" s="6">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="K48" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="K49" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="K50" s="6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="K51" s="6">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="K52" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="K53" s="6">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="K54" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="K55" s="6">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="K56" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="K57" s="6">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="K58" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="K59" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="K60" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="K61" s="6">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="K62" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="K63" s="6">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="K64" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="K65" s="6">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="K66" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="K67" s="6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="K68" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="K69" s="6">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="K70" s="6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="K71" s="6">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="K72" s="6">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="K73" s="6">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="K74" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="K75" s="6">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="K76" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="K77" s="6">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="K78" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="K79" s="6">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="K80" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="K81" s="6">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="K82" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="K83" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="K84" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="K85" s="6">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="K86" s="6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="K87" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="K88" s="6">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="K89" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="K90" s="6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="K91" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="K92" s="6">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="K93" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="K94" s="6">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="K95" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A96" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="K96" s="6">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="K97" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="K98" s="6">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="K99" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="K100" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="K101" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3BB5EC-9DD8-43D3-859D-3A686ECAACE0}">
+  <dimension ref="A2:E101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="23.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="26.25" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="19">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="19">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B13" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E13" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" t="s">
+        <v>266</v>
+      </c>
+      <c r="E14" s="19">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D15" t="s">
+        <v>269</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" t="s">
+        <v>251</v>
+      </c>
+      <c r="D19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" s="19">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C21" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" t="s">
+        <v>287</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" t="s">
+        <v>289</v>
+      </c>
+      <c r="C22" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" t="s">
+        <v>290</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>291</v>
+      </c>
+      <c r="B23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23" t="s">
+        <v>293</v>
+      </c>
+      <c r="E23" s="19">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B24" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" t="s">
+        <v>296</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" t="s">
+        <v>251</v>
+      </c>
+      <c r="D25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25" s="19">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B26" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" t="s">
+        <v>232</v>
+      </c>
+      <c r="D26" t="s">
+        <v>302</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>303</v>
+      </c>
+      <c r="B27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27" t="s">
+        <v>236</v>
+      </c>
+      <c r="D27" t="s">
+        <v>305</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>306</v>
+      </c>
+      <c r="B28" t="s">
+        <v>307</v>
+      </c>
+      <c r="C28" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" t="s">
+        <v>308</v>
+      </c>
+      <c r="E28" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" t="s">
+        <v>310</v>
+      </c>
+      <c r="E29" s="19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>311</v>
+      </c>
+      <c r="B30" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>314</v>
+      </c>
+      <c r="B31" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" t="s">
+        <v>316</v>
+      </c>
+      <c r="E31" s="19">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" t="s">
+        <v>319</v>
+      </c>
+      <c r="E32" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>320</v>
+      </c>
+      <c r="B33" t="s">
+        <v>321</v>
+      </c>
+      <c r="C33" t="s">
+        <v>236</v>
+      </c>
+      <c r="D33" t="s">
+        <v>322</v>
+      </c>
+      <c r="E33" s="19">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" t="s">
+        <v>325</v>
+      </c>
+      <c r="E34" s="19">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" t="s">
+        <v>327</v>
+      </c>
+      <c r="C35" t="s">
+        <v>228</v>
+      </c>
+      <c r="D35" t="s">
+        <v>328</v>
+      </c>
+      <c r="E35" s="19">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" t="s">
+        <v>330</v>
+      </c>
+      <c r="C36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" t="s">
+        <v>331</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>332</v>
+      </c>
+      <c r="B37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C37" t="s">
+        <v>251</v>
+      </c>
+      <c r="D37" t="s">
+        <v>334</v>
+      </c>
+      <c r="E37" s="19">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>335</v>
+      </c>
+      <c r="B38" t="s">
+        <v>336</v>
+      </c>
+      <c r="C38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D38" t="s">
+        <v>337</v>
+      </c>
+      <c r="E38" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>338</v>
+      </c>
+      <c r="B39" t="s">
+        <v>339</v>
+      </c>
+      <c r="C39" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" t="s">
+        <v>340</v>
+      </c>
+      <c r="E39" s="19">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>341</v>
+      </c>
+      <c r="B40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" t="s">
+        <v>343</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>344</v>
+      </c>
+      <c r="B41" t="s">
+        <v>345</v>
+      </c>
+      <c r="C41" t="s">
+        <v>228</v>
+      </c>
+      <c r="D41" t="s">
+        <v>346</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>347</v>
+      </c>
+      <c r="B42" t="s">
+        <v>348</v>
+      </c>
+      <c r="C42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" t="s">
+        <v>349</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>350</v>
+      </c>
+      <c r="B43" t="s">
+        <v>351</v>
+      </c>
+      <c r="C43" t="s">
+        <v>251</v>
+      </c>
+      <c r="D43" t="s">
+        <v>352</v>
+      </c>
+      <c r="E43" s="19">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>353</v>
+      </c>
+      <c r="B44" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" t="s">
+        <v>232</v>
+      </c>
+      <c r="D44" t="s">
+        <v>355</v>
+      </c>
+      <c r="E44" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>356</v>
+      </c>
+      <c r="B45" t="s">
+        <v>357</v>
+      </c>
+      <c r="C45" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" t="s">
+        <v>358</v>
+      </c>
+      <c r="E45" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>359</v>
+      </c>
+      <c r="B46" t="s">
+        <v>360</v>
+      </c>
+      <c r="C46" t="s">
+        <v>247</v>
+      </c>
+      <c r="D46" t="s">
+        <v>361</v>
+      </c>
+      <c r="E46" s="19">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>362</v>
+      </c>
+      <c r="B47" t="s">
+        <v>363</v>
+      </c>
+      <c r="C47" t="s">
+        <v>228</v>
+      </c>
+      <c r="D47" t="s">
+        <v>364</v>
+      </c>
+      <c r="E47" s="19">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>365</v>
+      </c>
+      <c r="B48" t="s">
+        <v>366</v>
+      </c>
+      <c r="C48" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" t="s">
+        <v>367</v>
+      </c>
+      <c r="E48" s="19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>368</v>
+      </c>
+      <c r="B49" t="s">
+        <v>369</v>
+      </c>
+      <c r="C49" t="s">
+        <v>251</v>
+      </c>
+      <c r="D49" t="s">
+        <v>370</v>
+      </c>
+      <c r="E49" s="19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>371</v>
+      </c>
+      <c r="B50" t="s">
+        <v>372</v>
+      </c>
+      <c r="C50" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" t="s">
+        <v>373</v>
+      </c>
+      <c r="E50" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>374</v>
+      </c>
+      <c r="B51" t="s">
+        <v>375</v>
+      </c>
+      <c r="C51" t="s">
+        <v>236</v>
+      </c>
+      <c r="D51" t="s">
+        <v>376</v>
+      </c>
+      <c r="E51" s="19">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s">
+        <v>378</v>
+      </c>
+      <c r="C52" t="s">
+        <v>247</v>
+      </c>
+      <c r="D52" t="s">
+        <v>379</v>
+      </c>
+      <c r="E52" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>380</v>
+      </c>
+      <c r="B53" t="s">
+        <v>381</v>
+      </c>
+      <c r="C53" t="s">
+        <v>228</v>
+      </c>
+      <c r="D53" t="s">
+        <v>382</v>
+      </c>
+      <c r="E53" s="19">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>383</v>
+      </c>
+      <c r="B54" t="s">
+        <v>384</v>
+      </c>
+      <c r="C54" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" t="s">
+        <v>385</v>
+      </c>
+      <c r="E54" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>386</v>
+      </c>
+      <c r="B55" t="s">
+        <v>387</v>
+      </c>
+      <c r="C55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D55" t="s">
+        <v>388</v>
+      </c>
+      <c r="E55" s="19">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>389</v>
+      </c>
+      <c r="B56" t="s">
+        <v>390</v>
+      </c>
+      <c r="C56" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" t="s">
+        <v>391</v>
+      </c>
+      <c r="E56" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>392</v>
+      </c>
+      <c r="B57" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" t="s">
+        <v>394</v>
+      </c>
+      <c r="E57" s="19">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>395</v>
+      </c>
+      <c r="B58" t="s">
+        <v>396</v>
+      </c>
+      <c r="C58" t="s">
+        <v>247</v>
+      </c>
+      <c r="D58" t="s">
+        <v>397</v>
+      </c>
+      <c r="E58" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>398</v>
+      </c>
+      <c r="B59" t="s">
+        <v>399</v>
+      </c>
+      <c r="C59" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" t="s">
+        <v>400</v>
+      </c>
+      <c r="E59" s="19">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>401</v>
+      </c>
+      <c r="B60" t="s">
+        <v>402</v>
+      </c>
+      <c r="C60" t="s">
+        <v>240</v>
+      </c>
+      <c r="D60" t="s">
+        <v>403</v>
+      </c>
+      <c r="E60" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>404</v>
+      </c>
+      <c r="B61" t="s">
+        <v>405</v>
+      </c>
+      <c r="C61" t="s">
+        <v>251</v>
+      </c>
+      <c r="D61" t="s">
+        <v>406</v>
+      </c>
+      <c r="E61" s="19">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>407</v>
+      </c>
+      <c r="B62" t="s">
+        <v>408</v>
+      </c>
+      <c r="C62" t="s">
+        <v>232</v>
+      </c>
+      <c r="D62" t="s">
+        <v>409</v>
+      </c>
+      <c r="E62" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>410</v>
+      </c>
+      <c r="B63" t="s">
+        <v>411</v>
+      </c>
+      <c r="C63" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" t="s">
+        <v>412</v>
+      </c>
+      <c r="E63" s="19">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>413</v>
+      </c>
+      <c r="B64" t="s">
+        <v>414</v>
+      </c>
+      <c r="C64" t="s">
+        <v>247</v>
+      </c>
+      <c r="D64" t="s">
+        <v>269</v>
+      </c>
+      <c r="E64" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>415</v>
+      </c>
+      <c r="B65" t="s">
+        <v>416</v>
+      </c>
+      <c r="C65" t="s">
+        <v>228</v>
+      </c>
+      <c r="D65" t="s">
+        <v>417</v>
+      </c>
+      <c r="E65" s="19">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>418</v>
+      </c>
+      <c r="B66" t="s">
+        <v>419</v>
+      </c>
+      <c r="C66" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" t="s">
+        <v>420</v>
+      </c>
+      <c r="E66" s="19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>421</v>
+      </c>
+      <c r="B67" t="s">
+        <v>422</v>
+      </c>
+      <c r="C67" t="s">
+        <v>251</v>
+      </c>
+      <c r="D67" t="s">
+        <v>423</v>
+      </c>
+      <c r="E67" s="19">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>424</v>
+      </c>
+      <c r="B68" t="s">
+        <v>425</v>
+      </c>
+      <c r="C68" t="s">
+        <v>232</v>
+      </c>
+      <c r="D68" t="s">
+        <v>426</v>
+      </c>
+      <c r="E68" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>427</v>
+      </c>
+      <c r="B69" t="s">
+        <v>428</v>
+      </c>
+      <c r="C69" t="s">
+        <v>236</v>
+      </c>
+      <c r="D69" t="s">
+        <v>429</v>
+      </c>
+      <c r="E69" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>430</v>
+      </c>
+      <c r="B70" t="s">
+        <v>431</v>
+      </c>
+      <c r="C70" t="s">
+        <v>247</v>
+      </c>
+      <c r="D70" t="s">
+        <v>432</v>
+      </c>
+      <c r="E70" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>433</v>
+      </c>
+      <c r="B71" t="s">
+        <v>434</v>
+      </c>
+      <c r="C71" t="s">
+        <v>228</v>
+      </c>
+      <c r="D71" t="s">
+        <v>435</v>
+      </c>
+      <c r="E71" s="19">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>436</v>
+      </c>
+      <c r="B72" t="s">
+        <v>437</v>
+      </c>
+      <c r="C72" t="s">
+        <v>240</v>
+      </c>
+      <c r="D72" t="s">
+        <v>349</v>
+      </c>
+      <c r="E72" s="19">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>438</v>
+      </c>
+      <c r="B73" t="s">
+        <v>439</v>
+      </c>
+      <c r="C73" t="s">
+        <v>251</v>
+      </c>
+      <c r="D73" t="s">
+        <v>440</v>
+      </c>
+      <c r="E73" s="19">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>441</v>
+      </c>
+      <c r="B74" t="s">
+        <v>442</v>
+      </c>
+      <c r="C74" t="s">
+        <v>232</v>
+      </c>
+      <c r="D74" t="s">
+        <v>443</v>
+      </c>
+      <c r="E74" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>444</v>
+      </c>
+      <c r="B75" t="s">
+        <v>445</v>
+      </c>
+      <c r="C75" t="s">
+        <v>236</v>
+      </c>
+      <c r="D75" t="s">
+        <v>446</v>
+      </c>
+      <c r="E75" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>447</v>
+      </c>
+      <c r="B76" t="s">
+        <v>448</v>
+      </c>
+      <c r="C76" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76" t="s">
+        <v>449</v>
+      </c>
+      <c r="E76" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>450</v>
+      </c>
+      <c r="B77" t="s">
+        <v>451</v>
+      </c>
+      <c r="C77" t="s">
+        <v>228</v>
+      </c>
+      <c r="D77" t="s">
+        <v>452</v>
+      </c>
+      <c r="E77" s="19">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>453</v>
+      </c>
+      <c r="B78" t="s">
+        <v>454</v>
+      </c>
+      <c r="C78" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" t="s">
+        <v>296</v>
+      </c>
+      <c r="E78" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>455</v>
+      </c>
+      <c r="B79" t="s">
+        <v>456</v>
+      </c>
+      <c r="C79" t="s">
+        <v>251</v>
+      </c>
+      <c r="D79" t="s">
+        <v>457</v>
+      </c>
+      <c r="E79" s="19">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>458</v>
+      </c>
+      <c r="B80" t="s">
+        <v>459</v>
+      </c>
+      <c r="C80" t="s">
+        <v>232</v>
+      </c>
+      <c r="D80" t="s">
+        <v>460</v>
+      </c>
+      <c r="E80" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>461</v>
+      </c>
+      <c r="B81" t="s">
+        <v>462</v>
+      </c>
+      <c r="C81" t="s">
+        <v>236</v>
+      </c>
+      <c r="D81" t="s">
+        <v>463</v>
+      </c>
+      <c r="E81" s="19">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>464</v>
+      </c>
+      <c r="B82" t="s">
+        <v>465</v>
+      </c>
+      <c r="C82" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82" t="s">
+        <v>466</v>
+      </c>
+      <c r="E82" s="19">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>467</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>468</v>
+      </c>
+      <c r="B84" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" t="s">
+        <v>232</v>
+      </c>
+      <c r="D84" t="s">
+        <v>233</v>
+      </c>
+      <c r="E84" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>469</v>
+      </c>
+      <c r="B85" t="s">
+        <v>235</v>
+      </c>
+      <c r="C85" t="s">
+        <v>236</v>
+      </c>
+      <c r="D85" t="s">
+        <v>237</v>
+      </c>
+      <c r="E85" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>470</v>
+      </c>
+      <c r="B86" t="s">
+        <v>239</v>
+      </c>
+      <c r="C86" t="s">
+        <v>240</v>
+      </c>
+      <c r="D86" t="s">
+        <v>241</v>
+      </c>
+      <c r="E86" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>471</v>
+      </c>
+      <c r="B87" t="s">
+        <v>472</v>
+      </c>
+      <c r="C87" t="s">
+        <v>228</v>
+      </c>
+      <c r="D87" t="s">
+        <v>229</v>
+      </c>
+      <c r="E87" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>473</v>
+      </c>
+      <c r="B88" t="s">
+        <v>474</v>
+      </c>
+      <c r="C88" t="s">
+        <v>236</v>
+      </c>
+      <c r="D88" t="s">
+        <v>237</v>
+      </c>
+      <c r="E88" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>475</v>
+      </c>
+      <c r="B89" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" t="s">
+        <v>232</v>
+      </c>
+      <c r="D89" t="s">
+        <v>233</v>
+      </c>
+      <c r="E89" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>476</v>
+      </c>
+      <c r="B90" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" t="s">
+        <v>240</v>
+      </c>
+      <c r="D90" t="s">
+        <v>241</v>
+      </c>
+      <c r="E90" s="19">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>477</v>
+      </c>
+      <c r="B91" t="s">
+        <v>262</v>
+      </c>
+      <c r="C91" t="s">
+        <v>251</v>
+      </c>
+      <c r="D91" t="s">
+        <v>263</v>
+      </c>
+      <c r="E91" s="19">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>478</v>
+      </c>
+      <c r="B92" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" t="s">
+        <v>240</v>
+      </c>
+      <c r="D92" t="s">
+        <v>260</v>
+      </c>
+      <c r="E92" s="19">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>479</v>
+      </c>
+      <c r="B93" t="s">
+        <v>231</v>
+      </c>
+      <c r="C93" t="s">
+        <v>232</v>
+      </c>
+      <c r="D93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E93" s="19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>480</v>
+      </c>
+      <c r="B94" t="s">
+        <v>235</v>
+      </c>
+      <c r="C94" t="s">
+        <v>236</v>
+      </c>
+      <c r="D94" t="s">
+        <v>237</v>
+      </c>
+      <c r="E94" s="19">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>481</v>
+      </c>
+      <c r="B95" t="s">
+        <v>246</v>
+      </c>
+      <c r="C95" t="s">
+        <v>247</v>
+      </c>
+      <c r="D95" t="s">
+        <v>248</v>
+      </c>
+      <c r="E95" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A96" t="s">
+        <v>484</v>
+      </c>
+      <c r="B96" t="s">
+        <v>250</v>
+      </c>
+      <c r="C96" t="s">
+        <v>251</v>
+      </c>
+      <c r="D96" t="s">
+        <v>252</v>
+      </c>
+      <c r="E96" s="19">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>485</v>
+      </c>
+      <c r="B97" t="s">
+        <v>254</v>
+      </c>
+      <c r="C97" t="s">
+        <v>232</v>
+      </c>
+      <c r="D97" t="s">
+        <v>255</v>
+      </c>
+      <c r="E97" s="19">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>486</v>
+      </c>
+      <c r="B98" t="s">
+        <v>243</v>
+      </c>
+      <c r="C98" t="s">
+        <v>228</v>
+      </c>
+      <c r="D98" t="s">
+        <v>244</v>
+      </c>
+      <c r="E98" s="19">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>487</v>
+      </c>
+      <c r="B99" t="s">
+        <v>246</v>
+      </c>
+      <c r="C99" t="s">
+        <v>247</v>
+      </c>
+      <c r="D99" t="s">
+        <v>248</v>
+      </c>
+      <c r="E99" s="19">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>488</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" t="s">
+        <v>228</v>
+      </c>
+      <c r="D100" t="s">
+        <v>229</v>
+      </c>
+      <c r="E100" s="19">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>489</v>
+      </c>
+      <c r="B101" t="s">
+        <v>268</v>
+      </c>
+      <c r="C101" t="s">
+        <v>236</v>
+      </c>
+      <c r="D101" t="s">
+        <v>269</v>
+      </c>
+      <c r="E101" s="19">
+        <v>0.97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F383A5E-E840-473F-BA2B-FA137CD05977}">
   <dimension ref="A1:N101"/>
